--- a/ReportWebSite/Reports1NF/Templates/reyting_zvit.xlsx
+++ b/ReportWebSite/Reports1NF/Templates/reyting_zvit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DKVSOURCESFINALEDITION_v20\ReportWebSite\Reports1NF\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6933F737-E14D-452B-96E5-B5D850E445F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB057E2B-D72A-4416-9EBB-9DCF7AE5638D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
   <si>
     <t>№ з/п</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>Місячна орендна плата</t>
+  </si>
+  <si>
+    <t>Узагальнений (інтегрований) показник у відсотках</t>
   </si>
 </sst>
 </file>
@@ -403,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -444,62 +447,65 @@
     <xf numFmtId="1" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -782,7 +788,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
@@ -798,83 +804,88 @@
     <col min="13" max="18" width="4.28515625" customWidth="1"/>
     <col min="19" max="19" width="4.140625" customWidth="1"/>
     <col min="20" max="20" width="7.28515625" customWidth="1"/>
-    <col min="21" max="21" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="8.85546875" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-    </row>
-    <row r="2" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+    </row>
+    <row r="2" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="23" t="s">
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="24"/>
-      <c r="L2" s="28" t="s">
+      <c r="K2" s="17"/>
+      <c r="L2" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="14" t="s">
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" s="27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+    <row r="3" spans="1:22" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
@@ -917,10 +928,11 @@
       <c r="S3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-    </row>
-    <row r="4" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+    </row>
+    <row r="4" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -984,8 +996,11 @@
       <c r="U4" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V4" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1016,9 +1031,10 @@
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
-      <c r="U5" s="13"/>
-    </row>
-    <row r="6" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U5" s="6"/>
+      <c r="V5" s="13"/>
+    </row>
+    <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -1049,9 +1065,10 @@
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
-      <c r="U6" s="13"/>
-    </row>
-    <row r="7" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U6" s="6"/>
+      <c r="V6" s="13"/>
+    </row>
+    <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -1082,9 +1099,10 @@
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
-      <c r="U7" s="13"/>
-    </row>
-    <row r="8" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U7" s="6"/>
+      <c r="V7" s="13"/>
+    </row>
+    <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -1115,9 +1133,10 @@
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
-      <c r="U8" s="13"/>
-    </row>
-    <row r="9" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U8" s="6"/>
+      <c r="V8" s="13"/>
+    </row>
+    <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -1148,9 +1167,10 @@
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
-      <c r="U9" s="13"/>
-    </row>
-    <row r="10" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U9" s="6"/>
+      <c r="V9" s="13"/>
+    </row>
+    <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -1181,9 +1201,10 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="13"/>
-    </row>
-    <row r="11" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U10" s="6"/>
+      <c r="V10" s="13"/>
+    </row>
+    <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -1214,9 +1235,10 @@
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
-      <c r="U11" s="13"/>
-    </row>
-    <row r="12" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U11" s="6"/>
+      <c r="V11" s="13"/>
+    </row>
+    <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -1247,9 +1269,10 @@
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
-      <c r="U12" s="13"/>
-    </row>
-    <row r="13" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U12" s="6"/>
+      <c r="V12" s="13"/>
+    </row>
+    <row r="13" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -1280,9 +1303,10 @@
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
-      <c r="U13" s="13"/>
-    </row>
-    <row r="14" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U13" s="6"/>
+      <c r="V13" s="13"/>
+    </row>
+    <row r="14" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -1313,13 +1337,14 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="13"/>
-    </row>
-    <row r="15" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="U14" s="6"/>
+      <c r="V14" s="13"/>
+    </row>
+    <row r="15" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
@@ -1345,23 +1370,25 @@
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
-    </row>
-    <row r="16" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="V15" s="7"/>
+    </row>
+    <row r="16" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="L2:S2"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="R1:V1"/>
     <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="U2:U3"/>
   </mergeCells>
   <pageMargins left="0.70833330000000005" right="0.70833330000000005" top="0.74791660000000004" bottom="0.74791660000000004" header="0.3152778" footer="0.3152778"/>
   <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>

--- a/ReportWebSite/Reports1NF/Templates/reyting_zvit.xlsx
+++ b/ReportWebSite/Reports1NF/Templates/reyting_zvit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DKVSOURCESFINALEDITION_v20\ReportWebSite\Reports1NF\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB057E2B-D72A-4416-9EBB-9DCF7AE5638D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A9766-04DA-4896-88EB-696239AAD123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,9 +130,6 @@
 </t>
   </si>
   <si>
-    <t>Кількість договорів з проблемами, %</t>
-  </si>
-  <si>
     <t>Узагальнений (інтегрований) показник</t>
   </si>
   <si>
@@ -146,6 +143,9 @@
   </si>
   <si>
     <t>Узагальнений (інтегрований) показник у відсотках</t>
+  </si>
+  <si>
+    <t>Кількість договорів без проблем, %</t>
   </si>
 </sst>
 </file>
@@ -861,7 +861,7 @@
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="22"/>
@@ -870,14 +870,14 @@
       <c r="Q2" s="23"/>
       <c r="R2" s="23"/>
       <c r="S2" s="24"/>
-      <c r="T2" s="27" t="s">
+      <c r="T2" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="27" t="s">
         <v>32</v>
-      </c>
-      <c r="U2" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" s="27" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -899,7 +899,7 @@
         <v>26</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>24</v>
@@ -926,7 +926,7 @@
         <v>19</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T3" s="28"/>
       <c r="U3" s="28"/>
